--- a/src/attributions/attributions_ig_traj_82.xlsx
+++ b/src/attributions/attributions_ig_traj_82.xlsx
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2332953701045559</v>
+        <v>0.05322159524110916</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,25 +1011,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01696128544291254</v>
+        <v>-0.02329537860512288</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06856166578804093</v>
+        <v>-0.01682480423965703</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3050925977563839</v>
+        <v>0.1323815551544214</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.04788675786692552</v>
+        <v>-0.06617656175674919</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1745299874901763</v>
+        <v>-0.0292115549411873</v>
       </c>
       <c r="S2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1042328497332236</v>
+        <v>0.02042133062050506</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,52 +1065,52 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01199259551909643</v>
+        <v>-0.03851400884494602</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.02602853288366473</v>
+        <v>-0.008432994404737328</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.05109286846831915</v>
+        <v>-0.03285655015215417</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.07326273848174572</v>
+        <v>-0.04418506277669167</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.01509153741078851</v>
+        <v>0.01835290308230703</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04977010937689253</v>
+        <v>0.02536622596312566</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,25 +1119,25 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.02569091810712523</v>
+        <v>-0.00582381311715646</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.03489534725284704</v>
+        <v>0.001319840101924666</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.4019285715394568</v>
+        <v>0.153685773179005</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1817158704630198</v>
+        <v>-0.03413229514410626</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1155,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.1048545932218355</v>
+        <v>-0.003117535805650992</v>
       </c>
       <c r="BC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.03887499065297684</v>
+        <v>-0.01423346930545537</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.06993059069889433</v>
+        <v>-0.03025792440881386</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,178 +1182,178 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0.09328110915889204</v>
+        <v>-0.03491458216588248</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.01137782389887682</v>
+        <v>0.02497411620882099</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
         <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.2201682824347131</v>
+        <v>0.07579764658639945</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.05129574046462667</v>
+        <v>0.02834994749004149</v>
       </c>
       <c r="BU2" t="n">
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2806308406858904</v>
+        <v>0.0874716912244973</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX2" t="n">
         <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.03185648009447709</v>
+        <v>-0.03384327427807378</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>-0.01338752911591737</v>
+        <v>-0.02445928495795955</v>
       </c>
       <c r="CD2" t="n">
         <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1141460088254104</v>
+        <v>-0.04038812049219669</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.008905235856516088</v>
+        <v>0.01853962218832658</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0813380124370686</v>
+        <v>0.02181709708639133</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01435922754042312</v>
+        <v>-0.0362860190567336</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.05808591236067093</v>
+        <v>0.007176873952673885</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.008554948762218724</v>
+        <v>0.01274485249089033</v>
       </c>
       <c r="CV2" t="n">
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.1186008382603216</v>
+        <v>-0.0406665803736922</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.00607367629787228</v>
+        <v>0.009976553854201277</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.05901625074053585</v>
+        <v>0.02459461373858537</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.1618005465304499</v>
+        <v>-0.07889213287818099</v>
       </c>
       <c r="DG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05308970628970495</v>
+        <v>0.004440111826546978</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.0386348140581884</v>
+        <v>0.0002342974966829706</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.04925092266500275</v>
+        <v>-0.01789569258049008</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
@@ -1362,25 +1362,25 @@
         <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.06831145570818677</v>
+        <v>0.02486990676933362</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0.0241020604391625</v>
+        <v>0.02842390048725537</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1683124043464669</v>
+        <v>-0.02143355540370577</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
@@ -1389,10 +1389,10 @@
         <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.008637107718921904</v>
+        <v>-0.02707789341240801</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1401,22 +1401,22 @@
         <v>-0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.03924956942119807</v>
+        <v>0.002725932273248776</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.07178653429223192</v>
+        <v>-0.02875209687600185</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
         <v>0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.03164859151616266</v>
+        <v>-0.008500549932163181</v>
       </c>
       <c r="EK2" t="n">
         <v>-0</v>
@@ -1425,97 +1425,97 @@
         <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.1158710773417946</v>
+        <v>0.01670995532312572</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.050897134189718</v>
+        <v>-0.01733729982537078</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.03085907331247343</v>
+        <v>0.02224296068615317</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.04781031119224126</v>
+        <v>0.03071336894269116</v>
       </c>
       <c r="EX2" t="n">
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.1235785901709618</v>
+        <v>-0.05523976128557095</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0002580707424343078</v>
+        <v>0.009695591708413675</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.05577873056653924</v>
+        <v>0.02127241404357405</v>
       </c>
       <c r="FG2" t="n">
         <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.01276096312976278</v>
+        <v>0.04250875473753681</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
         <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.05855743204801458</v>
+        <v>-0.008398917088092192</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.02889505165479432</v>
+        <v>0.03761085257289752</v>
       </c>
       <c r="FP2" t="n">
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01246971079960427</v>
+        <v>-0.01119205842956353</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
@@ -1524,25 +1524,25 @@
         <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.003663750043819337</v>
+        <v>0.01004838448162774</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.01085045161967639</v>
+        <v>0.002430350096981401</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.07665654274515049</v>
+        <v>-0.02734649207612479</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1551,10 +1551,10 @@
         <v>-0</v>
       </c>
       <c r="GC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1563,7 +1563,7 @@
         <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0.06537995516653258</v>
+        <v>-0.01242182007892046</v>
       </c>
     </row>
     <row r="3">
@@ -2709,52 +2709,52 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.3107181658316272</v>
+        <v>0.00280241071117585</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02976183197466981</v>
+        <v>-0.00141569701218768</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1089181402345552</v>
+        <v>-0.001465062387174411</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3302584820222674</v>
+        <v>0.007082617096912113</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02825186627542952</v>
+        <v>-0.002571888215397299</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.151789881411773</v>
+        <v>-0.004289611759049607</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2763,22 +2763,22 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.144097412044897</v>
+        <v>-0.0001384333420400126</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1192934849905792</v>
+        <v>-0.002513026426094998</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.03582591913338262</v>
+        <v>0.0001783905378310458</v>
       </c>
       <c r="Z5" t="n">
         <v>-0</v>
@@ -2787,64 +2787,64 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.111938198532726</v>
+        <v>-0.002075798669919221</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.06891180794846247</v>
+        <v>-0.003404021356063749</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.007874992180588052</v>
+        <v>2.905164144408178e-07</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.05442387994615624</v>
+        <v>-8.08473590348208e-05</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.03662718346129588</v>
+        <v>-0.0006340523076648193</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.04408780541395883</v>
+        <v>0.0001103396226050532</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3889169223815113</v>
+        <v>0.007571722427611335</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
@@ -2853,25 +2853,25 @@
         <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1248313835413273</v>
+        <v>-0.0004987045327086426</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.212670887687977</v>
+        <v>-0.0005960243471702482</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.06153536150635553</v>
+        <v>-0.001297654891349196</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,13 +2880,13 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.1093347263335778</v>
+        <v>-0.001574232366070876</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.00583425322384413</v>
+        <v>-0.0006491987824552365</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,25 +2895,25 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.03084231173901917</v>
+        <v>0.001783096394436477</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.06088361335801287</v>
+        <v>0.004780445817820347</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.09032817548396981</v>
+        <v>-0.0006169336994796658</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,52 +2922,52 @@
         <v>-0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2007610812890766</v>
+        <v>0.004461994686421607</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.06973345118274878</v>
+        <v>-0.0003957759164580574</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.1127718733048004</v>
+        <v>-0.0005953242906967682</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.1212988825164547</v>
+        <v>-0.001160996953867592</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.005417125945245017</v>
+        <v>0.001082795603385928</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.06415212799316655</v>
+        <v>0.0006210236938176703</v>
       </c>
       <c r="CK5" t="n">
         <v>-0</v>
@@ -2976,37 +2976,37 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.02478674206125636</v>
+        <v>-0.001891072591578002</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.06844748443487526</v>
+        <v>0.0001073736783435678</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.01110338373231354</v>
+        <v>-0.0007660922334892812</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.1134612067608359</v>
+        <v>-0.001333754745437142</v>
       </c>
       <c r="CX5" t="n">
         <v>-0</v>
@@ -3015,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.03201399282957606</v>
+        <v>0.000526294689074976</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.07369116918489647</v>
+        <v>0.001098467569208859</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.1327486932150359</v>
+        <v>-0.001823428725511421</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
@@ -3042,25 +3042,25 @@
         <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.03343444082744317</v>
+        <v>-0.002150825758286829</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.01865091493637253</v>
+        <v>0.0003024915828157454</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.04261432628975774</v>
+        <v>0.0008875083829804056</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
@@ -3069,40 +3069,40 @@
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.02666698192324661</v>
+        <v>0.0005138767865326802</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.01409836475492657</v>
+        <v>0.001732099894267863</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.1537431790890832</v>
+        <v>-0.001808275673526199</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.003475030533211908</v>
+        <v>5.957696388860274e-05</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.02857536895009037</v>
+        <v>0.002095854047510133</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3111,25 +3111,25 @@
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.04773616490797271</v>
+        <v>-0.0008374030121536802</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.007373688342398373</v>
+        <v>0.0003259409820332134</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.1027058546723979</v>
+        <v>-3.419526572418062e-05</v>
       </c>
       <c r="EM5" t="n">
         <v>0</v>
@@ -3141,49 +3141,49 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.08419215416467166</v>
+        <v>-0.0007351127325199197</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
         <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.08735358421727883</v>
+        <v>-0.0004720446154339132</v>
       </c>
       <c r="ET5" t="n">
         <v>-0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.04622208832402133</v>
+        <v>0.0005227685060162924</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.1194508212141385</v>
+        <v>-0.001786726747175951</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.04313556389995044</v>
+        <v>0.0002813153250007841</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.080300595491509</v>
+        <v>0.0007362445943503752</v>
       </c>
       <c r="FE5" t="n">
         <v>-0</v>
@@ -3192,64 +3192,64 @@
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0005758533472516611</v>
+        <v>0.001362850277760146</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.01533983601259457</v>
+        <v>-0.00105179999180355</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.01122221905033754</v>
+        <v>-0.001308665587569629</v>
       </c>
       <c r="FN5" t="n">
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.01300456028405107</v>
+        <v>-9.580156791654536e-05</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0009310833793891327</v>
+        <v>0.0003424595763154579</v>
       </c>
       <c r="FU5" t="n">
         <v>-0</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.05051051856303174</v>
+        <v>0.00186642220167811</v>
       </c>
       <c r="FW5" t="n">
         <v>-0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.06283966387512338</v>
+        <v>-0.0008866591622904648</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3258,19 +3258,19 @@
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
-        <v>-0.01928284664266222</v>
+        <v>0.00224360081773366</v>
       </c>
       <c r="GF5" t="n">
         <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3847,49 +3847,49 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4882286098625775</v>
+        <v>0.3982190224429981</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3493060096212742</v>
+        <v>-0.3292788012848291</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02676210604847647</v>
+        <v>-0.03620730732346609</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4719971815945482</v>
+        <v>0.5522878630980326</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3592208256988224</v>
+        <v>-0.3936067256291581</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.09454309483162013</v>
+        <v>-0.101108968365338</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -3898,25 +3898,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2110626018427641</v>
+        <v>0.2180369983921208</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.01728250871950817</v>
+        <v>-0.0568866643207888</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1731899692097161</v>
+        <v>-0.02482449523542928</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -3925,52 +3925,52 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1191974022835985</v>
+        <v>-0.06493116384478718</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002956455043470465</v>
+        <v>-0.1105331591660457</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.001824197307364991</v>
+        <v>-0.06288742743354168</v>
       </c>
       <c r="AG7" t="n">
         <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02372103716121936</v>
+        <v>0.2356274817122749</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1040499049579073</v>
+        <v>-0.07634700850928415</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.06101218418891219</v>
+        <v>0.1591189387263667</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3982,43 +3982,43 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.521783398022534</v>
+        <v>0.4552583122754142</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.08251340071932887</v>
+        <v>-0.2240989802758873</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1938131556146309</v>
+        <v>-0.1823228766406053</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.04559960281153577</v>
+        <v>-0.07287395750995297</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.1227551954973371</v>
+        <v>-0.1565240962531101</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1569624871599662</v>
+        <v>-0.1035709696841175</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.05167378146342187</v>
+        <v>-0.0719994395107517</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.06350282815398646</v>
+        <v>0.09569922109321412</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.2252501183609297</v>
+        <v>-0.004336973155666138</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,73 +4063,73 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2770500840048498</v>
+        <v>0.5241679558681233</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.003984791352354891</v>
+        <v>-0.164866433934868</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.1419807414754423</v>
+        <v>-0.04117315272490422</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.1532085283485708</v>
+        <v>-0.1919672849974636</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.05197341564500706</v>
+        <v>0.2010148306194562</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.03269896028559296</v>
+        <v>-0.03754800921639483</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.004737188691362844</v>
+        <v>-0.1519294124896384</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1925100094852468</v>
+        <v>0.421769616344947</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1509810715415653</v>
+        <v>0.1744436570646541</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,28 +4138,28 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.1453273343928873</v>
+        <v>-0.1929166516872139</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.09245419350633609</v>
+        <v>0.2072632639460677</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.03162842272909083</v>
+        <v>-0.01031921702053443</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
@@ -4171,46 +4171,46 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.1326238028571796</v>
+        <v>-0.290869965197888</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01177950708157313</v>
+        <v>0.1011142145363045</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.02020473672636965</v>
+        <v>-0.1144130879717983</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.005570460096400613</v>
+        <v>-0.08384471348129953</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.1142529811954348</v>
+        <v>0.05216634635810403</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.09996581407363851</v>
+        <v>0.009945613493136397</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4222,79 +4222,79 @@
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.06802829690655253</v>
+        <v>-0.01721629968475781</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.003862392276417253</v>
+        <v>-0.1489444831434723</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.03181454285339198</v>
+        <v>-0.1617709946448953</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1454254834319706</v>
+        <v>-0.1601066082119645</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07043852983578734</v>
+        <v>0.1840000742178383</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.1022587287372753</v>
+        <v>0.008797745549868586</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.1457686915856674</v>
+        <v>-0.1765974643009905</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.07529148136218708</v>
+        <v>0.08696336111928452</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.008013022281075963</v>
+        <v>0.04408967246947498</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,106 +4306,106 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.1447617265706236</v>
+        <v>-0.2363730763621623</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.05895472197836762</v>
+        <v>0.2375503169078464</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.035017077032135</v>
+        <v>-0.02623454165086979</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.02229300997985641</v>
+        <v>-0.1635019782812017</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.133195459604736</v>
+        <v>0.1628574181291498</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.01497178857795096</v>
+        <v>0.06989592108202487</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.007053697419970867</v>
+        <v>-0.03466483518687868</v>
       </c>
       <c r="FR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.05885783436985463</v>
+        <v>0.05312387665543161</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0006815740829485001</v>
+        <v>0.03577242486637942</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.03010909127683131</v>
+        <v>-0.2645473118920376</v>
       </c>
       <c r="GA7" t="n">
         <v>-0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.1218908080271759</v>
+        <v>0.1426076905384153</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
         <v>-0</v>
@@ -4416,22 +4416,22 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.231449532817269</v>
+        <v>0.523585315777525</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02602322050085849</v>
+        <v>-0.004617365156587006</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1398131571070172</v>
+        <v>-0.1594070735141114</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
@@ -4443,76 +4443,76 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2116385028745053</v>
+        <v>0.8157901904296009</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02342288765170563</v>
+        <v>-0.1124509363575274</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2220543394636216</v>
+        <v>-0.2259406909338778</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>-0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.04246209509597979</v>
+        <v>0.2218952845638948</v>
       </c>
       <c r="U8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.04079366521686396</v>
+        <v>-0.1121641400407757</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02203602072491659</v>
+        <v>-0.0208158922711741</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
         <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0360054280256781</v>
+        <v>0.03552476893118946</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.03300217694965268</v>
+        <v>-0.3330426779284129</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0008519130326991404</v>
+        <v>-0.1773928249319013</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI8" t="n">
         <v>-0</v>
@@ -4521,22 +4521,22 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02510397344991293</v>
+        <v>0.1799196241169179</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.01383255895856471</v>
+        <v>0.04703951698545934</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.05491635321977517</v>
+        <v>-0.1273955350714293</v>
       </c>
       <c r="AQ8" t="n">
         <v>-0</v>
@@ -4548,10 +4548,10 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.1927712051469155</v>
+        <v>0.8829119049288371</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
@@ -4560,13 +4560,13 @@
         <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.03398318466189342</v>
+        <v>-0.1366886217900328</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0.1371372767845399</v>
+        <v>-0.2755702639072961</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
         <v>-0</v>
@@ -4578,73 +4578,73 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.07341745866832408</v>
+        <v>-0.0329857723131743</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF8" t="n">
         <v>0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.04037282880675956</v>
+        <v>-0.1615815375168504</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.04105674093204414</v>
+        <v>-0.04791965477731782</v>
       </c>
       <c r="BI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.07484272843651277</v>
+        <v>0.06431151416612463</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.01664173703562849</v>
+        <v>0.137316349477154</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.01953274941900041</v>
+        <v>-0.04555707900928418</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>-0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1101803944239804</v>
+        <v>0.6629253092704654</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
         <v>0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.0216952321110461</v>
+        <v>-0.0260925399095645</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0.05189314895563132</v>
+        <v>-0.1754738623145795</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
@@ -4659,7 +4659,7 @@
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.06383465070856573</v>
+        <v>-0.272725189433983</v>
       </c>
       <c r="CF8" t="n">
         <v>0</v>
@@ -4668,52 +4668,52 @@
         <v>-0</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.01187677874890978</v>
+        <v>0.02797925952996618</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.05728364794327888</v>
+        <v>0.1417721322145868</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.01738421990519874</v>
+        <v>-0.5026475008811906</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.01326820673287472</v>
+        <v>0.2368149337266383</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.02525089470375305</v>
+        <v>0.2484997503861778</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
         <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.05259872699058874</v>
+        <v>-0.2622730639139481</v>
       </c>
       <c r="CX8" t="n">
         <v>-0</v>
@@ -4722,13 +4722,13 @@
         <v>0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.0125576442849181</v>
+        <v>-0.008997228677288841</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.06199085078588337</v>
+        <v>0.131223245983309</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.06085770333485389</v>
+        <v>-0.161236008861724</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
@@ -4749,52 +4749,52 @@
         <v>-0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.03195048598017653</v>
+        <v>-0.4454587048556861</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0006660263362072598</v>
+        <v>0.07262650700636522</v>
       </c>
       <c r="DK8" t="n">
         <v>0</v>
       </c>
       <c r="DL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.02039671385414045</v>
+        <v>-0.1416968644235007</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.02068240529148602</v>
+        <v>0.06620289659270807</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.00527219390041246</v>
+        <v>0.03354392245250425</v>
       </c>
       <c r="DT8" t="n">
         <v>0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW8" t="n">
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.05016294788921499</v>
+        <v>0.001614101995070155</v>
       </c>
       <c r="DY8" t="n">
         <v>0</v>
@@ -4803,10 +4803,10 @@
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01899071819336802</v>
+        <v>0.1014622042137325</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.03761491852852761</v>
+        <v>-0.1352211573763731</v>
       </c>
       <c r="EC8" t="n">
         <v>-0</v>
@@ -4821,22 +4821,22 @@
         <v>-0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.04346520639092642</v>
+        <v>-0.0614563172872912</v>
       </c>
       <c r="EH8" t="n">
         <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.004594869148549702</v>
+        <v>-0.08712730249636268</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.03909524480897765</v>
+        <v>0.04262141171056226</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
@@ -4845,22 +4845,22 @@
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.02680086748811106</v>
+        <v>-0.1256755343796135</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
         <v>-0</v>
       </c>
       <c r="ES8" t="n">
-        <v>-0.02103375033263492</v>
+        <v>-0.1512683614149095</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.03693007654662391</v>
+        <v>0.08523802378799385</v>
       </c>
       <c r="EU8" t="n">
         <v>-0</v>
@@ -4869,13 +4869,13 @@
         <v>0</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX8" t="n">
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.05376618620818475</v>
+        <v>-0.2989242288007387</v>
       </c>
       <c r="EZ8" t="n">
         <v>0</v>
@@ -4884,25 +4884,25 @@
         <v>-0</v>
       </c>
       <c r="FB8" t="n">
-        <v>-0.008677473487327645</v>
+        <v>-0.03403647268163319</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.06021680086869257</v>
+        <v>0.1269183828045037</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.006629406474221709</v>
+        <v>-0.3355910857704396</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
@@ -4911,25 +4911,25 @@
         <v>-0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.03940674981484957</v>
+        <v>0.1445016434261406</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.04944927289797777</v>
+        <v>0.1148381948248975</v>
       </c>
       <c r="FM8" t="n">
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.00599498073300684</v>
+        <v>-0.04515612614217829</v>
       </c>
       <c r="FR8" t="n">
         <v>-0</v>
@@ -4938,28 +4938,28 @@
         <v>-0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.006385529933991085</v>
+        <v>0.01703629998626935</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.04169894456325476</v>
+        <v>0.02959917738970604</v>
       </c>
       <c r="FV8" t="n">
         <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.02021749811674222</v>
+        <v>-0.117278627974665</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
         <v>-0</v>
@@ -4968,16 +4968,16 @@
         <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.04617970682211346</v>
+        <v>-0.01953138499652912</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
       </c>
       <c r="GF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5551,100 +5551,100 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4001686762298062</v>
+        <v>0.01694378366340177</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5159006436192732</v>
+        <v>-0.005766541714263014</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.07873333470691944</v>
+        <v>-0.004962389252398261</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2756489100235527</v>
+        <v>0.02530369659748377</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5343532966935378</v>
+        <v>-0.01526170446830385</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3144857595395151</v>
+        <v>-0.01459122167084962</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3061308033766915</v>
+        <v>0.01102875282995267</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1597305177040074</v>
+        <v>-0.01228800597918125</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.04825412413785513</v>
+        <v>-0.005292701085302037</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2266943237783364</v>
+        <v>-0.005802604697500796</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.1950448762278785</v>
+        <v>-0.01264168894722139</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -5653,34 +5653,34 @@
         <v>-0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.09352691846122628</v>
+        <v>0.002246240605068216</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1258649589799902</v>
+        <v>0.007794342977749651</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1045379434475945</v>
+        <v>0.0001850469145452139</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.07808699114072805</v>
+        <v>-0.001066675652776338</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,7 +5689,7 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.8668851609817694</v>
+        <v>0.02694876651803661</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,16 +5698,16 @@
         <v>-0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.04007301025399031</v>
+        <v>-0.003314667299825937</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.2623290032615823</v>
+        <v>-0.006624355949277802</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0.05585686323084793</v>
+        <v>-0.00551175966179485</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.3588898986606902</v>
+        <v>-0.01235314178321432</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
         <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>-0.1498664949848927</v>
+        <v>-0.0005771222311850832</v>
       </c>
       <c r="BK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5538699842633923</v>
+        <v>0.007606704144982003</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,43 +5752,43 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.4864621215528249</v>
+        <v>0.01556544133511224</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.2244949824960894</v>
+        <v>0.00615769555827942</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.5470424339908312</v>
+        <v>0.02520234756489409</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.09759819039208856</v>
+        <v>-0.002403354156490009</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.1696704308535649</v>
+        <v>-0.009099913977771429</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -5797,70 +5797,70 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.1070202200280966</v>
+        <v>-0.004620183268634705</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.09783827707330915</v>
+        <v>0.003855771230942149</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.04176838274777327</v>
+        <v>0.002796775962608126</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.3241209954199962</v>
+        <v>-0.008171569582202762</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.4158470458616803</v>
+        <v>0.01136948009856394</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0.1341663044247065</v>
+        <v>0.002733171425024241</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.04267894798918033</v>
+        <v>-0.004530183765268999</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.06946477961922405</v>
+        <v>0.003768617207834935</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,52 +5869,52 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.004624778099504242</v>
+        <v>0.004961089644574761</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.5412209041271064</v>
+        <v>-0.004656936303719052</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1347144560847658</v>
+        <v>0.0009759128380668795</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.1658464544988005</v>
+        <v>0.0008979049212225868</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1017549402236388</v>
+        <v>-0.007730888579871809</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.01393357221063471</v>
+        <v>-0.002604498787376841</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,16 +5923,16 @@
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1983664996227667</v>
+        <v>0.002427921838462828</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.07413439978399194</v>
+        <v>0.004986203998037374</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,34 +5941,34 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.007939011521398483</v>
+        <v>-0.008299163941454057</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.02645707410225241</v>
+        <v>-0.008959239072569557</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.08306095000796687</v>
+        <v>0.004327918426359461</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.1508468751513619</v>
+        <v>-0.002721993867288486</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,16 +5977,16 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.02918013735743002</v>
+        <v>-0.001274881770209851</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.06253453905252539</v>
+        <v>-0.002439030852489797</v>
       </c>
       <c r="EQ10" t="n">
         <v>0</v>
@@ -5995,34 +5995,34 @@
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0372940463589946</v>
+        <v>-0.004091752865537261</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.07502145165239887</v>
+        <v>0.002979607265957166</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
         <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.02857053036401418</v>
+        <v>-0.004930362554252402</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.06201553480535634</v>
+        <v>0.0008459967470002198</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,43 +6031,43 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.05038047156539201</v>
+        <v>0.004566593809772234</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.1778235466788308</v>
+        <v>0.0006858863992480638</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.0396609680701673</v>
+        <v>0.009314405702394666</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
       </c>
       <c r="FM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.03275358102115473</v>
+        <v>-0.003526439998675969</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.006062675627954728</v>
+        <v>-0.0007366208921775801</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,25 +6076,25 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.02472591231236161</v>
+        <v>0.002347422068430938</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0.2359631837601204</v>
+        <v>0.004751202380317992</v>
       </c>
       <c r="FX10" t="n">
         <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.2913142755491064</v>
+        <v>-0.007440585271441944</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
@@ -6103,16 +6103,16 @@
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0.2283653159742479</v>
+        <v>-0.003449458710630958</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
@@ -6120,49 +6120,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.2997521493821963</v>
+        <v>-0.2125383104367259</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6670171176451951</v>
+        <v>0.4167327847035644</v>
       </c>
       <c r="C11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1970431586795605</v>
+        <v>-0.09450776412774413</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2147439267659787</v>
+        <v>-0.1801881856941732</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5417324225927</v>
+        <v>0.5813216393879104</v>
       </c>
       <c r="L11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4450219104143522</v>
+        <v>-0.1376226129554306</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -6174,19 +6174,19 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02790575441034306</v>
+        <v>0.06183583729094665</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3889975715489097</v>
+        <v>-0.001101119164965716</v>
       </c>
       <c r="U11" t="n">
         <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1182154928231543</v>
+        <v>0.03958082598635561</v>
       </c>
       <c r="X11" t="n">
         <v>-0</v>
@@ -6195,106 +6195,106 @@
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.009806241548659139</v>
+        <v>-0.05478993946648993</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1521009631118795</v>
+        <v>-0.01272372309219086</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.07735421193763947</v>
+        <v>-0.07002218534677893</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
         <v>-0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.1170385635826632</v>
+        <v>-0.02867536207857972</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.2477543621450191</v>
+        <v>0.1112402351302333</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.02135426708340405</v>
+        <v>-0.07884127964702556</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.1825032247390035</v>
+        <v>-0.04429599125836026</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.7046411152950731</v>
+        <v>0.2446056257120466</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.2985285977666551</v>
+        <v>-0.1462437529513565</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>-0.2018624539477467</v>
+        <v>-0.1566283435218798</v>
       </c>
       <c r="BD11" t="n">
-        <v>-0.01263263144262765</v>
+        <v>0.08915968745173324</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.4024644869109993</v>
+        <v>-0.03167676661746884</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,16 +6303,16 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0.08981971825472129</v>
+        <v>0.06218737342631589</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1408114805182554</v>
+        <v>0.1099133969466879</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
@@ -6321,13 +6321,13 @@
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.3641262165406196</v>
+        <v>0.1141911480695221</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
@@ -6336,73 +6336,73 @@
         <v>-0</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.1388563344212244</v>
+        <v>0.03865059727333337</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.5133368196230956</v>
+        <v>0.2848519648125321</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX11" t="n">
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.04344319934800958</v>
+        <v>-0.01706963931766433</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0619235834610161</v>
+        <v>0.085569818683718</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.1433000049060328</v>
+        <v>-0.1786675542492493</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.01153534219610146</v>
+        <v>0.0126636320855823</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
         <v>-0</v>
       </c>
       <c r="CK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL11" t="n">
         <v>-0</v>
       </c>
       <c r="CM11" t="n">
-        <v>-0.2771848578597977</v>
+        <v>0.001771917564208718</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.1183622134044223</v>
+        <v>-0.2565829923391659</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.3045988322845404</v>
+        <v>-0.009008625542315945</v>
       </c>
       <c r="CR11" t="n">
         <v>-0</v>
@@ -6414,22 +6414,22 @@
         <v>-0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.03056683758198033</v>
+        <v>0.07815398933030078</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.161600687649504</v>
+        <v>-0.1859885194274539</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0135809195033081</v>
+        <v>-0.0139243078529161</v>
       </c>
       <c r="DA11" t="n">
         <v>0</v>
@@ -6438,43 +6438,43 @@
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2917427840649627</v>
+        <v>0.09153693839979021</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.5228519181239446</v>
+        <v>-0.263848627076605</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.06316924743805104</v>
+        <v>-0.04825863798230037</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0.1663204951195936</v>
+        <v>-0.04080627364576107</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.2381630467071555</v>
+        <v>-0.1045068208974418</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
@@ -6483,25 +6483,25 @@
         <v>-0</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.04753044652951902</v>
+        <v>-0.01880510297852146</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT11" t="n">
         <v>0</v>
       </c>
       <c r="DU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV11" t="n">
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0.05667080589281725</v>
+        <v>0.1403070041824008</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.1349199257235902</v>
+        <v>0.1017343788618148</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,25 +6510,25 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.1188221727374267</v>
+        <v>0.06439866641800299</v>
       </c>
       <c r="EB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0.07000491586962793</v>
+        <v>0.02405855479786779</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.1862933391201466</v>
+        <v>-0.1196251692499956</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.003830900903749491</v>
+        <v>-0.02937716199272921</v>
       </c>
       <c r="EK11" t="n">
         <v>-0</v>
@@ -6552,19 +6552,19 @@
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>-0.0143701094551972</v>
+        <v>-0.02824459186961242</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.1246645186903523</v>
+        <v>-0.1133797933920759</v>
       </c>
       <c r="EQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.05099301672039378</v>
+        <v>-0.01232581139173608</v>
       </c>
       <c r="ET11" t="n">
         <v>-0</v>
@@ -6576,13 +6576,13 @@
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.05473948428792864</v>
+        <v>0.08655403056893118</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.1523755514133901</v>
+        <v>-0.2181354936301569</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
@@ -6591,7 +6591,7 @@
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.06278753289593536</v>
+        <v>-0.02124065467729939</v>
       </c>
       <c r="FC11" t="n">
         <v>-0</v>
@@ -6603,13 +6603,13 @@
         <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.1722323188365705</v>
+        <v>0.05315813035633508</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.08474000121619571</v>
+        <v>-0.02087570987628395</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.09477325793104015</v>
+        <v>0.06763067010404504</v>
       </c>
       <c r="FL11" t="n">
         <v>0</v>
@@ -6630,40 +6630,40 @@
         <v>-0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.008554537453408452</v>
+        <v>-0.07528433781365534</v>
       </c>
       <c r="FQ11" t="n">
-        <v>-0.0358571532023528</v>
+        <v>0.01914059454029614</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.003298426106906461</v>
+        <v>0.0288468280216889</v>
       </c>
       <c r="FU11" t="n">
         <v>-0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0.08276711158247461</v>
+        <v>0.05528525518219839</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.185131670278037</v>
+        <v>-0.1490829056320322</v>
       </c>
       <c r="GA11" t="n">
         <v>-0</v>
@@ -6675,7 +6675,7 @@
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6692,7 +6692,7 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4945887217873191</v>
+        <v>0.2738705583578963</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,13 +6701,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1811161944600052</v>
+        <v>-0.1940594066363757</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4497633571465519</v>
+        <v>-0.08990867472684506</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -6716,25 +6716,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3266283592880189</v>
+        <v>0.3787475470624568</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2159931598792174</v>
+        <v>-0.1783096510121454</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3779141855761516</v>
+        <v>-0.1381004067564182</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6746,76 +6746,76 @@
         <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.197605538855979</v>
+        <v>0.03453263793174607</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2899961565515073</v>
+        <v>-0.04465191310425055</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-0.1022310855888482</v>
+        <v>0.04934973179167218</v>
       </c>
       <c r="Z12" t="n">
         <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.2015859634797505</v>
+        <v>-0.05933137415937813</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.07442228857153688</v>
+        <v>-0.08990468645245231</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0.03441862996789023</v>
+        <v>0.01492610571345345</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
         <v>-0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.04053019855205228</v>
+        <v>0.1768823898690136</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.04652238762083605</v>
+        <v>0.08217181818385599</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.1013103920219183</v>
+        <v>0.01617057671540979</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -6827,7 +6827,7 @@
         <v>-0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5375292070967715</v>
+        <v>0.4163112920095983</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
@@ -6836,16 +6836,16 @@
         <v>-0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08487879274508932</v>
+        <v>0.0097850677403953</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.2014871789834176</v>
+        <v>0.01308659963206965</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,22 +6854,22 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.1268106334154435</v>
+        <v>-0.1607502976204533</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1224552512682073</v>
+        <v>-0.1916775125086769</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0.2236015612420611</v>
+        <v>-0.0528849399831244</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -6878,10 +6878,10 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1050440180017935</v>
+        <v>-0.04628821185312453</v>
       </c>
       <c r="BN12" t="n">
         <v>0</v>
@@ -6890,13 +6890,13 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.3056496704363769</v>
+        <v>0.1016407517859961</v>
       </c>
       <c r="BQ12" t="n">
         <v>-0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.08812691697629738</v>
+        <v>0.07081384647657639</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,34 +6908,34 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2509256467562377</v>
+        <v>0.3242937289004807</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.01705415631913215</v>
+        <v>-0.02486798636160833</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>-0.1178852241932192</v>
+        <v>0.005050482234589054</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.14407089493221</v>
+        <v>-0.1287538068004605</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
@@ -6944,13 +6944,13 @@
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.0459145800960754</v>
+        <v>0.04244939281693655</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.09744933411253932</v>
+        <v>0.01106456594117301</v>
       </c>
       <c r="CK12" t="n">
         <v>-0</v>
@@ -6959,25 +6959,25 @@
         <v>-0</v>
       </c>
       <c r="CM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.2211977517155954</v>
+        <v>-0.2116030181787455</v>
       </c>
       <c r="CO12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.1240997738799082</v>
+        <v>0.03212531656769071</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0.06459507773574777</v>
+        <v>-0.09804521174358913</v>
       </c>
       <c r="CT12" t="n">
         <v>-0</v>
@@ -6986,25 +6986,25 @@
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1127478844935151</v>
+        <v>-0.1335588380234829</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.04555566506055841</v>
+        <v>0.0506284461227908</v>
       </c>
       <c r="DA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.09770152681155879</v>
+        <v>0.02047047715655584</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
@@ -7016,7 +7016,7 @@
         <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.4365554473683361</v>
+        <v>-0.1104993741741391</v>
       </c>
       <c r="DG12" t="n">
         <v>-0</v>
@@ -7025,16 +7025,16 @@
         <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.0909244103495148</v>
+        <v>0.03033000169127018</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0.06000934527004034</v>
+        <v>-0.06028523490022639</v>
       </c>
       <c r="DL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM12" t="n">
         <v>-0</v>
@@ -7043,49 +7043,49 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.07761742161332032</v>
+        <v>-0.0604677207064289</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.06531854780485312</v>
+        <v>0.0847223137020065</v>
       </c>
       <c r="DS12" t="n">
         <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>-0.02761512472370018</v>
+        <v>0.0708849655729767</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.1527202552337326</v>
+        <v>0.03235785909167434</v>
       </c>
       <c r="DY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ12" t="n">
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.1097229646934255</v>
+        <v>-0.05149878471600591</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.01786919965586809</v>
+        <v>-0.007476087835869253</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7094,25 +7094,25 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03276897996888584</v>
+        <v>-0.1321730657777835</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.09637008858672368</v>
+        <v>0.02409520755882106</v>
       </c>
       <c r="EK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.09705993587118641</v>
+        <v>-0.03025269476928241</v>
       </c>
       <c r="EM12" t="n">
         <v>-0</v>
@@ -7121,52 +7121,52 @@
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.05841192856429108</v>
+        <v>-0.09462569390851464</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02490257533066366</v>
+        <v>0.04239975476260308</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.0006737818749891012</v>
+        <v>-0.02707258413569117</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.1256010913832087</v>
+        <v>-0.1418406702391203</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.05239154725913782</v>
+        <v>0.03681211077416133</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.088380633875452</v>
+        <v>0.002015054315962328</v>
       </c>
       <c r="FE12" t="n">
         <v>-0</v>
@@ -7175,25 +7175,25 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02721371476470683</v>
+        <v>-0.07626145272177504</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.1474171625681975</v>
+        <v>-0.07815064231494635</v>
       </c>
       <c r="FL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.08977042735310241</v>
+        <v>-0.02600948950419038</v>
       </c>
       <c r="FN12" t="n">
         <v>-0</v>
@@ -7202,10 +7202,10 @@
         <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.004971443761288021</v>
+        <v>-0.03178682530371367</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,28 +7214,28 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.01929652189949167</v>
+        <v>-0.01605991772089713</v>
       </c>
       <c r="FU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.02516763427565074</v>
+        <v>0.09341100387050706</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.1352147534447707</v>
+        <v>-0.1244955868751619</v>
       </c>
       <c r="GA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
@@ -7244,10 +7244,10 @@
         <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.09834058565547901</v>
+        <v>0.0187234811985104</v>
       </c>
       <c r="GF12" t="n">
         <v>-0</v>
@@ -7258,10 +7258,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B13" t="n">
-        <v>1.011763126702376</v>
+        <v>0.7285203498443519</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.3165747429840345</v>
+        <v>-0.3818329939981981</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7282,13 +7282,13 @@
         <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4976760523760083</v>
+        <v>-0.1629576129798657</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7543645248753629</v>
+        <v>0.9010064817984766</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,25 +7297,25 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3163539261127508</v>
+        <v>-0.4058077414448121</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.4468502498800208</v>
+        <v>-0.15019195921175</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3189409744994327</v>
+        <v>0.112755068274848</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
@@ -7324,61 +7324,61 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01403900556412935</v>
+        <v>-0.1901334258981504</v>
       </c>
       <c r="X13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z13" t="n">
         <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>-0.08812823621462393</v>
+        <v>-0.1775517999074246</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.2320694839676748</v>
+        <v>0.05724477289456589</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.07368945468531282</v>
+        <v>-0.1686654034025368</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.06102431715823462</v>
+        <v>-0.008202435068039079</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1676043071566721</v>
+        <v>0.2540709713557643</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01681889901305281</v>
+        <v>0.0983632385873757</v>
       </c>
       <c r="AP13" t="n">
         <v>0</v>
@@ -7390,22 +7390,22 @@
         <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0.04056532359303154</v>
+        <v>-0.01606970282567442</v>
       </c>
       <c r="AT13" t="n">
         <v>-0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.8833462777320521</v>
+        <v>0.8312353503792912</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.03919743928738281</v>
+        <v>-0.1351825977120847</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
@@ -7414,16 +7414,16 @@
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.2529533153444525</v>
+        <v>0.002382724222785543</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1769609719053305</v>
+        <v>-0.1285557415818757</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.3446380212215771</v>
+        <v>-0.2171780368260541</v>
       </c>
       <c r="BH13" t="n">
         <v>0</v>
@@ -7441,16 +7441,16 @@
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0.2288504518030856</v>
+        <v>-0.08782727640974085</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1231952779541088</v>
+        <v>0.07690190502642374</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
@@ -7459,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.4043138505825423</v>
+        <v>0.2045931395444128</v>
       </c>
       <c r="BQ13" t="n">
         <v>-0</v>
@@ -7471,40 +7471,40 @@
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0.007331020905588625</v>
+        <v>0.1239189813800454</v>
       </c>
       <c r="BU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.6072543173942083</v>
+        <v>0.6087802985388795</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.08436678753474004</v>
+        <v>-0.2051698091747441</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>-0.1227202060607119</v>
+        <v>-0.1695716820240789</v>
       </c>
       <c r="CD13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.2382808936996956</v>
+        <v>-0.3183589644110997</v>
       </c>
       <c r="CF13" t="n">
         <v>-0</v>
@@ -7513,37 +7513,37 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.002088584171360656</v>
+        <v>0.1010397827698081</v>
       </c>
       <c r="CI13" t="n">
         <v>-0</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.1745298211874899</v>
+        <v>0.06925397299721288</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.2749993930548091</v>
+        <v>-0.4837046319763706</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.2555836521925575</v>
+        <v>0.0439670816160584</v>
       </c>
       <c r="CR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7552,40 +7552,40 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.04278855124197548</v>
+        <v>0.02572320310761433</v>
       </c>
       <c r="CV13" t="n">
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.2069775854379398</v>
+        <v>-0.3113004157705246</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.01247027549480552</v>
+        <v>0.07832656819453346</v>
       </c>
       <c r="DA13" t="n">
         <v>0</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.1497907531439451</v>
+        <v>0.09322544756351164</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.5254555177713973</v>
+        <v>-0.2135115566831013</v>
       </c>
       <c r="DG13" t="n">
         <v>-0</v>
@@ -7594,7 +7594,7 @@
         <v>-0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1413700096189343</v>
+        <v>-0.04452828543260984</v>
       </c>
       <c r="DJ13" t="n">
         <v>-0</v>
@@ -7606,22 +7606,22 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.07715078650234251</v>
+        <v>-0.1003093388803144</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.1233050357300186</v>
+        <v>-0.1513797289894197</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.009378940925894164</v>
+        <v>0.04932982911929142</v>
       </c>
       <c r="DS13" t="n">
         <v>-0</v>
@@ -7633,13 +7633,13 @@
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>-0.0160044044265244</v>
+        <v>-0.1748379956339138</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.1648052995602487</v>
+        <v>0.1942342733294805</v>
       </c>
       <c r="DY13" t="n">
         <v>-0</v>
@@ -7648,7 +7648,7 @@
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.1216736366680187</v>
+        <v>-0.05583365317660372</v>
       </c>
       <c r="EB13" t="n">
         <v>-0</v>
@@ -7657,55 +7657,55 @@
         <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.05568947779455889</v>
+        <v>0.1969575559774066</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.0361449113385342</v>
+        <v>-0.1752139482838812</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.03936167744457823</v>
+        <v>-0.001966254506832045</v>
       </c>
       <c r="EK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.2011178814294263</v>
+        <v>0.04667596833165766</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.1407502838647246</v>
+        <v>-0.1726151596950138</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.05179623093798153</v>
+        <v>0.06498199672900298</v>
       </c>
       <c r="ET13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU13" t="n">
         <v>0</v>
@@ -7714,13 +7714,13 @@
         <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.05813581741753918</v>
+        <v>0.1066090774889752</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.2423099157119345</v>
+        <v>-0.3652126195516969</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
@@ -7729,25 +7729,25 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.01000217972589195</v>
+        <v>0.07132862767473987</v>
       </c>
       <c r="FC13" t="n">
         <v>-0</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.138983347705345</v>
+        <v>0.09469764720927795</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.1367755253307322</v>
+        <v>-0.1466703777865849</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,73 +7756,73 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.1190693488997032</v>
+        <v>-0.002582629028666291</v>
       </c>
       <c r="FL13" t="n">
         <v>0</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
         <v>-0</v>
       </c>
       <c r="FO13" t="n">
-        <v>-0.1009883915129364</v>
+        <v>-0.1098104959013847</v>
       </c>
       <c r="FP13" t="n">
         <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01727348557558478</v>
+        <v>-0.0258225058673109</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01165686833771001</v>
+        <v>0.02748582561599536</v>
       </c>
       <c r="FU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.03585855828510186</v>
+        <v>-0.03348723643676117</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.2440895327251988</v>
+        <v>-0.1966053470015503</v>
       </c>
       <c r="GA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC13" t="n">
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0.02223776331063541</v>
+        <v>0.05805480699518448</v>
       </c>
     </row>
     <row r="14">
@@ -8399,16 +8399,16 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4384947136024657</v>
+        <v>-0.5620481685215344</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5645430942875664</v>
+        <v>0.2940817795391043</v>
       </c>
       <c r="D15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1551409449946548</v>
+        <v>0.2782608738135182</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
@@ -8426,43 +8426,43 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.354901471396478</v>
+        <v>-0.6968935035019614</v>
       </c>
       <c r="L15" t="n">
-        <v>0.41028599952497</v>
+        <v>0.3109456691680389</v>
       </c>
       <c r="M15" t="n">
         <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4142356552794316</v>
+        <v>0.2485766166678902</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1702469538061594</v>
+        <v>-0.1222794567117417</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.01073786436869537</v>
+        <v>-0.06225079640905632</v>
       </c>
       <c r="V15" t="n">
         <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.02253876921035746</v>
+        <v>-0.04034407968534639</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -8471,79 +8471,79 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1752997753759625</v>
+        <v>-0.05237787044977038</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0.01211110896770389</v>
+        <v>0.1204048515334125</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.1356271840149547</v>
+        <v>0.01606769312677449</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.2553302090699681</v>
+        <v>-0.2239524146698164</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.08157467934765703</v>
+        <v>0.03075611744460873</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.005231567907129052</v>
+        <v>-0.2460200379832899</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.5136470344013092</v>
+        <v>-0.6266640995393485</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.3289629074724532</v>
+        <v>0.04027975768523593</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.06395675400375711</v>
+        <v>0.02165656760045555</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
@@ -8552,28 +8552,28 @@
         <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.01794020934429201</v>
+        <v>0.29546614667202</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.1765326958229029</v>
+        <v>0.2164689323600344</v>
       </c>
       <c r="BF15" t="n">
         <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.511840733904689</v>
+        <v>0.3390085049538845</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI15" t="n">
         <v>0</v>
@@ -8588,25 +8588,25 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.132512469572002</v>
+        <v>0.02748416442109879</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.07067015596357397</v>
+        <v>-0.01304957819371374</v>
       </c>
       <c r="BO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.2492842350812189</v>
+        <v>0.0006754199086277278</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
         <v>0</v>
@@ -8615,19 +8615,19 @@
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.213052409475797</v>
+        <v>-0.4725937254859742</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.3256010615675581</v>
+        <v>0.03777980001945622</v>
       </c>
       <c r="BX15" t="n">
         <v>-0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.04387742635761212</v>
+        <v>-0.00381288909826027</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA15" t="n">
         <v>0</v>
@@ -8639,19 +8639,19 @@
         <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.0992704405291116</v>
+        <v>0.2804849800976911</v>
       </c>
       <c r="CF15" t="n">
-        <v>-0.0527130482163712</v>
+        <v>-0.09092923944860569</v>
       </c>
       <c r="CG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.06398015960785459</v>
+        <v>-0.05545087938154657</v>
       </c>
       <c r="CI15" t="n">
         <v>0</v>
@@ -8660,7 +8660,7 @@
         <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>0</v>
@@ -8669,16 +8669,16 @@
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.02230701693190685</v>
+        <v>0.3577878718601155</v>
       </c>
       <c r="CO15" t="n">
-        <v>-0.01063438821268936</v>
+        <v>-0.08579946959483495</v>
       </c>
       <c r="CP15" t="n">
         <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.2216456591581533</v>
+        <v>-0.1153383228353477</v>
       </c>
       <c r="CR15" t="n">
         <v>0</v>
@@ -8693,19 +8693,19 @@
         <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.04862300897306415</v>
+        <v>0.2598365747680558</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0.06548826318079252</v>
+        <v>-0.07526038247832531</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.06824023481499125</v>
+        <v>-0.04814197303684873</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
@@ -8714,7 +8714,7 @@
         <v>-0</v>
       </c>
       <c r="DC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD15" t="n">
         <v>-0</v>
@@ -8723,52 +8723,52 @@
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.1839913823142336</v>
+        <v>0.05039455824488879</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.06450864131171612</v>
+        <v>-0.05690474403956071</v>
       </c>
       <c r="DH15" t="n">
         <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1017461709560372</v>
+        <v>0.0164526351218559</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.001281998847647639</v>
+        <v>0.1391315338713543</v>
       </c>
       <c r="DP15" t="n">
-        <v>-0.1336619290198794</v>
+        <v>-0.0788664352906337</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.07186357997485393</v>
+        <v>0.004354298961025667</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
@@ -8777,19 +8777,19 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.01114702460204591</v>
+        <v>-0.168497275564868</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.1962795853516722</v>
+        <v>-0.06237629354891753</v>
       </c>
       <c r="DZ15" t="n">
         <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.04783134027460437</v>
+        <v>0.07971705848041676</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
@@ -8801,19 +8801,19 @@
         <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.03830051660178573</v>
+        <v>0.1774536177534827</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0.01604447258788491</v>
+        <v>0.07663199511389036</v>
       </c>
       <c r="EI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.1059562249770709</v>
+        <v>-0.05316617307094276</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
@@ -8828,55 +8828,55 @@
         <v>0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.05119050485141856</v>
+        <v>0.1830560232329319</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.06083607557816</v>
+        <v>0.0198231668967817</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.1135161576824377</v>
+        <v>-0.08147538093536867</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW15" t="n">
         <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.06729635489164136</v>
+        <v>0.3115826548188949</v>
       </c>
       <c r="EZ15" t="n">
-        <v>-0.05246926284480415</v>
+        <v>-0.08277221334035728</v>
       </c>
       <c r="FA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.07641878991241856</v>
+        <v>-0.06773234690229446</v>
       </c>
       <c r="FC15" t="n">
         <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
         <v>0</v>
@@ -8885,90 +8885,90 @@
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.1346019355947578</v>
+        <v>0.07151323817632482</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.1747293272063864</v>
+        <v>0.1396737133076779</v>
       </c>
       <c r="FJ15" t="n">
         <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.1687715315515015</v>
+        <v>0.1211200170320464</v>
       </c>
       <c r="FL15" t="n">
         <v>-0</v>
       </c>
       <c r="FM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.0004358151069170103</v>
+        <v>0.002168941117307782</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0.06857647230406907</v>
+        <v>-0.005665512282008052</v>
       </c>
       <c r="FS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.01014899207572082</v>
+        <v>-0.006818384021636563</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
         <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.03037638362880518</v>
+        <v>0.1548222141744575</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.05303290725837673</v>
+        <v>0.1228239734450555</v>
       </c>
       <c r="GB15" t="n">
         <v>0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2055062302758776</v>
+        <v>0.5371449286397615</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,10 +8977,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.06296283833481794</v>
+        <v>0.0156523410348615</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1173793847269422</v>
+        <v>-0.3240704049832474</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
@@ -8992,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1741983083243653</v>
+        <v>0.6410876527919589</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,64 +9004,64 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.02533298134164554</v>
+        <v>-0.1404750021032606</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0969737424786737</v>
+        <v>-0.374556384109565</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.01966832453687259</v>
+        <v>0.168277542308869</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.01800633461988629</v>
+        <v>-0.1097244450568446</v>
       </c>
       <c r="X16" t="n">
-        <v>0.005469790198724632</v>
+        <v>-0.0642618774302228</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.00296221917877459</v>
+        <v>-0.08437868900293256</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01760675474723862</v>
+        <v>-0.2981532475592725</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.005139818909455873</v>
+        <v>0.0971982862808197</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -9073,25 +9073,25 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.02056016413595503</v>
+        <v>0.1100895113904511</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.001399246776504192</v>
+        <v>-0.07708526008667095</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.03765856408717663</v>
+        <v>-0.0650309249396086</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
@@ -9100,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.1150679278862735</v>
+        <v>0.6545175509212477</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
@@ -9112,25 +9112,25 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.02189075952143523</v>
+        <v>-0.3244879622271429</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.06768536372293865</v>
+        <v>-0.2974650482504597</v>
       </c>
       <c r="AZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.03888085688545283</v>
+        <v>-0.1092449940056241</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,25 +9139,25 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.04369241631472425</v>
+        <v>0.02351193361657753</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.03699069351055441</v>
+        <v>-0.0559435476976865</v>
       </c>
       <c r="BI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
         <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.02839818555866282</v>
+        <v>0.1213359044114122</v>
       </c>
       <c r="BN16" t="n">
         <v>-0</v>
@@ -9166,37 +9166,37 @@
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.01127386212315208</v>
+        <v>0.05920281627730279</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01186476311039469</v>
+        <v>0.05198056101201791</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.06926009302663308</v>
+        <v>0.4235582298621791</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.02266213494695685</v>
+        <v>-0.08753873632996469</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.0200152355531692</v>
+        <v>-0.1563029392657149</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9211,34 +9211,34 @@
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.03539780498795846</v>
+        <v>-0.1726770450168101</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.001408625079305106</v>
+        <v>0.05197008802804867</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.026281331614003</v>
+        <v>0.09760261518271031</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.003433776272628785</v>
+        <v>-0.2356332437586972</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
@@ -9247,10 +9247,10 @@
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.01316465808895808</v>
+        <v>0.2404837789819356</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.04482779483835826</v>
+        <v>0.05150082524739837</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
@@ -9259,25 +9259,25 @@
         <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
         <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.03338997257051114</v>
+        <v>-0.1587342848768317</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.001115817383746189</v>
+        <v>0.02945267101988174</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03221796259263329</v>
+        <v>0.146263207053531</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9286,25 +9286,25 @@
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.02174187665985625</v>
+        <v>-0.1344849741543716</v>
       </c>
       <c r="DG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05561369450506172</v>
+        <v>-0.2020318325179619</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.0007709387805039835</v>
+        <v>0.06179799133199079</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
@@ -9313,13 +9313,13 @@
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
         <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.008285007831750955</v>
+        <v>-0.05837750843152311</v>
       </c>
       <c r="DP16" t="n">
         <v>0</v>
@@ -9328,16 +9328,16 @@
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.02190353624591798</v>
+        <v>0.01501939685576763</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.0001195746036537094</v>
+        <v>0.1329093500970825</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
       </c>
       <c r="DU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV16" t="n">
         <v>0</v>
@@ -9346,142 +9346,142 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.0338882460357494</v>
+        <v>-0.07267342587534607</v>
       </c>
       <c r="DY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ16" t="n">
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.006800529975173537</v>
+        <v>-0.0111152237722772</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.007259939018529627</v>
+        <v>0.02958774782454221</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
         <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.04106491493501332</v>
+        <v>-0.07355836946807275</v>
       </c>
       <c r="EH16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI16" t="n">
         <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.009608438038561174</v>
+        <v>0.005258875705992858</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.03792198451674606</v>
+        <v>0.0004211479550487069</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO16" t="n">
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.02561544427955326</v>
+        <v>-0.0831804014549631</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.009074469461897624</v>
+        <v>-0.1014142739088402</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.005210748961827335</v>
+        <v>-0.01440264216282588</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
         <v>0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.03267916023496451</v>
+        <v>-0.1979386056224754</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.0004481118777160255</v>
+        <v>0.006436190125168746</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.02772804836690708</v>
+        <v>0.1164407058008208</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
         <v>0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.01110881150690835</v>
+        <v>0.1417103953426644</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ16" t="n">
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.01156152095378102</v>
+        <v>-0.07838915695142026</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.03026237868498058</v>
+        <v>0.1918073940303404</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.002298596435556907</v>
+        <v>-0.05164982999598028</v>
       </c>
       <c r="FR16" t="n">
         <v>-0</v>
@@ -9490,37 +9490,37 @@
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.01189509514685068</v>
+        <v>0.09392151236117351</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.02007546584446118</v>
+        <v>-0.1279226940789442</v>
       </c>
       <c r="FV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.00357531190270161</v>
+        <v>-0.0327057927566061</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.0154499706255827</v>
+        <v>0.1938993061958267</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
@@ -9529,7 +9529,7 @@
         <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,22 +9537,22 @@
         <v>-0</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.3374306026109953</v>
+        <v>-0.2284665019787412</v>
       </c>
       <c r="C17" t="n">
         <v>-0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0502423444092687</v>
+        <v>0.08065603556854223</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8091658984004622</v>
+        <v>0.4791979731950208</v>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -9564,7 +9564,7 @@
         <v>-0</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2909191633465786</v>
+        <v>-0.2774184736609763</v>
       </c>
       <c r="L17" t="n">
         <v>-0</v>
@@ -9573,10 +9573,10 @@
         <v>-0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.01337441899121863</v>
+        <v>0.1872039981702149</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6941656809888945</v>
+        <v>0.6178635109619363</v>
       </c>
       <c r="P17" t="n">
         <v>-0</v>
@@ -9591,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.03594662030736007</v>
+        <v>-0.06370158958742562</v>
       </c>
       <c r="U17" t="n">
         <v>-0</v>
@@ -9600,10 +9600,10 @@
         <v>-0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.09139262485865764</v>
+        <v>0.09813309928668572</v>
       </c>
       <c r="X17" t="n">
-        <v>0.07070836100373644</v>
+        <v>0.07204991204193971</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -9615,10 +9615,10 @@
         <v>-0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.04071108654159751</v>
+        <v>0.02599746336569408</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -9627,52 +9627,52 @@
         <v>-0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.03206132289908045</v>
+        <v>0.2561523677715034</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.03885116749737612</v>
+        <v>0.05514496070697117</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK17" t="n">
         <v>-0</v>
       </c>
       <c r="AL17" t="n">
-        <v>-0.03347888550614748</v>
+        <v>-0.01385741296356448</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.01546285018883909</v>
+        <v>-0.0005424583137622472</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.1483786053787186</v>
+        <v>0.03751282673548131</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU17" t="n">
-        <v>-0.2619379693169241</v>
+        <v>-0.4274668230522092</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
@@ -9681,13 +9681,13 @@
         <v>-0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1587325660462941</v>
+        <v>0.09084301320450776</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.5493858530745045</v>
+        <v>0.37643932403096</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
         <v>0</v>
@@ -9696,10 +9696,10 @@
         <v>-0</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD17" t="n">
-        <v>-0.1644495617786421</v>
+        <v>0.02382190536296048</v>
       </c>
       <c r="BE17" t="n">
         <v>-0</v>
@@ -9708,64 +9708,64 @@
         <v>-0</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.03334645334765674</v>
+        <v>0.1070437778610252</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.1061260968733251</v>
+        <v>0.05190145564473143</v>
       </c>
       <c r="BI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ17" t="n">
         <v>0</v>
       </c>
       <c r="BK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM17" t="n">
-        <v>-0.1473220451232191</v>
+        <v>-0.08356385455781147</v>
       </c>
       <c r="BN17" t="n">
         <v>0</v>
       </c>
       <c r="BO17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>-0.05951756902958124</v>
+        <v>-0.1178677421294481</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.002220260349993671</v>
+        <v>0.0198519681740212</v>
       </c>
       <c r="BR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV17" t="n">
-        <v>-0.1213061964526997</v>
+        <v>-0.1852522413661901</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
         <v>-0</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.09559784864333409</v>
+        <v>0.01975820371979759</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.2660342382698038</v>
+        <v>0.2197686015594502</v>
       </c>
       <c r="CA17" t="n">
         <v>0</v>
@@ -9777,37 +9777,37 @@
         <v>0</v>
       </c>
       <c r="CD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.08138857651729396</v>
+        <v>0.07953693762043829</v>
       </c>
       <c r="CF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG17" t="n">
         <v>0</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.009376841250926615</v>
+        <v>-0.03383961510043772</v>
       </c>
       <c r="CI17" t="n">
-        <v>-0.1263505582024618</v>
+        <v>-0.136513186236563</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK17" t="n">
         <v>-0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
         <v>-0</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.01509434110607554</v>
+        <v>0.1390269792403424</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -9816,16 +9816,16 @@
         <v>0</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.1479330668738598</v>
+        <v>-0.08607040268526682</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.04558480581820458</v>
+        <v>-0.1679244086682896</v>
       </c>
       <c r="CS17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU17" t="n">
         <v>0</v>
@@ -9834,61 +9834,61 @@
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.05482058933012713</v>
+        <v>0.07692738433140776</v>
       </c>
       <c r="CX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY17" t="n">
         <v>-0</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.004585366525197714</v>
+        <v>-0.04239517808221356</v>
       </c>
       <c r="DA17" t="n">
-        <v>-0.1240952985657715</v>
+        <v>-0.1584388285137993</v>
       </c>
       <c r="DB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC17" t="n">
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE17" t="n">
         <v>-0</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.08697526527842013</v>
+        <v>0.06680139401407878</v>
       </c>
       <c r="DG17" t="n">
         <v>0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.04591916056388112</v>
+        <v>0.1486159701499825</v>
       </c>
       <c r="DJ17" t="n">
-        <v>-0.002179638146404585</v>
+        <v>-0.03074362117627545</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.02725694368313264</v>
+        <v>-0.07082633694308116</v>
       </c>
       <c r="DP17" t="n">
         <v>-0</v>
@@ -9897,37 +9897,37 @@
         <v>-0</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.06048250370340799</v>
+        <v>0.060580859566303</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0196107594272775</v>
+        <v>-0.009888934530458981</v>
       </c>
       <c r="DT17" t="n">
         <v>0</v>
       </c>
       <c r="DU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV17" t="n">
         <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.07872797930177589</v>
+        <v>0.06538667537712203</v>
       </c>
       <c r="DY17" t="n">
         <v>0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.06100857010638141</v>
+        <v>0.1169460610182328</v>
       </c>
       <c r="EB17" t="n">
-        <v>-0.06325387351678034</v>
+        <v>-0.07971734484686967</v>
       </c>
       <c r="EC17" t="n">
         <v>0</v>
@@ -9939,49 +9939,49 @@
         <v>0</v>
       </c>
       <c r="EF17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.04977103764035621</v>
+        <v>0.04000577300550584</v>
       </c>
       <c r="EH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ17" t="n">
-        <v>-0.003032765859472093</v>
+        <v>-0.06192378275697593</v>
       </c>
       <c r="EK17" t="n">
-        <v>-0.1204894559007509</v>
+        <v>-0.01290646091059651</v>
       </c>
       <c r="EL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM17" t="n">
         <v>0</v>
       </c>
       <c r="EN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.006730110823425828</v>
+        <v>0.0287177887013342</v>
       </c>
       <c r="EQ17" t="n">
         <v>0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES17" t="n">
-        <v>-0.04323829076264494</v>
+        <v>-0.06651757943401693</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.02255567655046177</v>
+        <v>-0.1502231722602516</v>
       </c>
       <c r="EU17" t="n">
         <v>-0</v>
@@ -9990,13 +9990,13 @@
         <v>-0</v>
       </c>
       <c r="EW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.04801215224340864</v>
+        <v>0.09577064115452898</v>
       </c>
       <c r="EZ17" t="n">
         <v>0</v>
@@ -10005,37 +10005,37 @@
         <v>0</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.03292266317893534</v>
+        <v>-0.003981420792247508</v>
       </c>
       <c r="FC17" t="n">
-        <v>-0.1244997306457424</v>
+        <v>-0.1318094545285251</v>
       </c>
       <c r="FD17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.01285297256217167</v>
+        <v>-0.155227947461396</v>
       </c>
       <c r="FI17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ17" t="n">
         <v>0</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.0366336767811095</v>
+        <v>0.0445198325977489</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0.1280715727300959</v>
+        <v>-0.1600111963359964</v>
       </c>
       <c r="FM17" t="n">
         <v>-0</v>
@@ -10050,7 +10050,7 @@
         <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.002633585223439075</v>
+        <v>0.04105586106809968</v>
       </c>
       <c r="FR17" t="n">
         <v>-0</v>
@@ -10059,25 +10059,25 @@
         <v>0</v>
       </c>
       <c r="FT17" t="n">
-        <v>-0.06401241497032328</v>
+        <v>-0.07130784541923334</v>
       </c>
       <c r="FU17" t="n">
-        <v>-0.1560363073533319</v>
+        <v>0.04219167211100888</v>
       </c>
       <c r="FV17" t="n">
         <v>0</v>
       </c>
       <c r="FW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX17" t="n">
         <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.04460305674436464</v>
+        <v>0.05292914410733084</v>
       </c>
       <c r="GA17" t="n">
         <v>-0</v>
@@ -10086,16 +10086,16 @@
         <v>0</v>
       </c>
       <c r="GC17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.0966687840145305</v>
+        <v>-0.05882420015605665</v>
       </c>
       <c r="GE17" t="n">
         <v>0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
         <v>-0</v>
